--- a/data/trans_orig/P25D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2386</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309642</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287249</t>
+          <t>287798</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598878</t>
+          <t>598677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30726</t>
+          <t>30362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489707</t>
+          <t>490946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515231</t>
+          <t>514697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504887</t>
+          <t>507727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>514814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002633</t>
+          <t>1002997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027858</t>
+          <t>1028010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305706</t>
+          <t>304870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315039</t>
+          <t>315067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>342296</t>
+          <t>342484</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348471</t>
+          <t>348481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650905</t>
+          <t>651004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662537</t>
+          <t>662513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304963</t>
+          <t>304237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>471398</t>
+          <t>470655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>778685</t>
+          <t>779446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>787557</t>
+          <t>787615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175330</t>
+          <t>174819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204582</t>
+          <t>204714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208273</t>
+          <t>208230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382226</t>
+          <t>381757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386604</t>
+          <t>386583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,97 +2445,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1798</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6995</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1798</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7248</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1798</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268245</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249808</t>
+          <t>250061</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520402</t>
+          <t>519531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>600634</t>
+          <t>600803</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>612618</t>
+          <t>612770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>825025</t>
+          <t>824480</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840156</t>
+          <t>840382</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1432629</t>
+          <t>1431426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1451040</t>
+          <t>1451317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,44 +3146,44 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>6653</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>13655</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6653</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>13662</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>29866</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>903739</t>
+          <t>904616</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>922637</t>
+          <t>923092</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,49 +3259,49 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>711078</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>704076</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>714400</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>711078</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>704069</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>714666</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1804</t>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1613737</t>
+          <t>1614772</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1635166</t>
+          <t>1635123</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82700</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3393171</t>
+          <t>3392381</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3426468</t>
+          <t>3426746</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3620078</t>
+          <t>3619224</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3640035</t>
+          <t>3640210</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7023108</t>
+          <t>7024272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7061281</t>
+          <t>7061674</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>478</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>478</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289193</t>
+          <t>315583</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287798</t>
+          <t>313335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>600635</t>
+          <t>634428</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598677</t>
+          <t>631882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,17 +1068,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>507439</t>
+          <t>519467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490946</t>
+          <t>502874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514697</t>
+          <t>526481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>513072</t>
+          <t>543945</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507727</t>
+          <t>536786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514814</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1020511</t>
+          <t>1063412</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002997</t>
+          <t>1046355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1028010</t>
+          <t>1071153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,22 +1411,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>312133</t>
+          <t>312207</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304870</t>
+          <t>304472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315067</t>
+          <t>315015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>346563</t>
+          <t>353776</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>342484</t>
+          <t>349959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348481</t>
+          <t>355718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>658695</t>
+          <t>665984</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651004</t>
+          <t>659366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662513</t>
+          <t>669503</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>310927</t>
+          <t>368148</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304237</t>
+          <t>354211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>474421</t>
+          <t>420671</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>470655</t>
+          <t>418009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>785347</t>
+          <t>788819</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>779446</t>
+          <t>773266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>787615</t>
+          <t>793788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>422</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178048</t>
+          <t>204885</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174819</t>
+          <t>200429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>207053</t>
+          <t>225548</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204714</t>
+          <t>223392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208230</t>
+          <t>226793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>385102</t>
+          <t>430432</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>381757</t>
+          <t>427362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386583</t>
+          <t>432072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>255258</t>
+          <t>261961</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250061</t>
+          <t>257190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>524894</t>
+          <t>532668</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519531</t>
+          <t>528010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>27779</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>608131</t>
+          <t>702122</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>600803</t>
+          <t>694538</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>612770</t>
+          <t>706596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>835130</t>
+          <t>756664</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>824480</t>
+          <t>746637</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840382</t>
+          <t>760722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1443261</t>
+          <t>1458787</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1431426</t>
+          <t>1447932</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1451317</t>
+          <t>1466373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>710836</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>710836</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>710836</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>842617</t>
+          <t>764875</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>842617</t>
+          <t>764875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>842617</t>
+          <t>764875</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1459192</t>
+          <t>1475711</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1459192</t>
+          <t>1475711</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1459192</t>
+          <t>1475711</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29866</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>915132</t>
+          <t>782974</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>904616</t>
+          <t>773936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923092</t>
+          <t>790247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>711078</t>
+          <t>823976</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>704076</t>
+          <t>817540</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>714400</t>
+          <t>828422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1626211</t>
+          <t>1606951</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1614772</t>
+          <t>1594836</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1635123</t>
+          <t>1615535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926906</t>
+          <t>796123</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926906</t>
+          <t>796123</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926906</t>
+          <t>796123</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644638</t>
+          <t>1627455</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644638</t>
+          <t>1627455</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644638</t>
+          <t>1627455</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36286</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>92172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3412888</t>
+          <t>3479357</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3392381</t>
+          <t>3459473</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3426746</t>
+          <t>3493456</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3631770</t>
+          <t>3702126</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3619224</t>
+          <t>3689029</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3640210</t>
+          <t>3710324</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7044657</t>
+          <t>7181482</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7024272</t>
+          <t>7157860</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7061674</t>
+          <t>7199274</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
